--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.96882031507216</v>
+        <v>2.757433301199226</v>
       </c>
       <c r="D2" t="n">
-        <v>17.54371138255507</v>
+        <v>2.850853099665199</v>
       </c>
       <c r="E2" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F2" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.87082350859988</v>
+        <v>5.504008820147481</v>
       </c>
       <c r="D3" t="n">
-        <v>18.3246608801872</v>
+        <v>2.977757393030421</v>
       </c>
       <c r="E3" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F3" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.10598212245978</v>
+        <v>4.079722094899715</v>
       </c>
       <c r="D4" t="n">
-        <v>16.86376664224523</v>
+        <v>2.74036207936485</v>
       </c>
       <c r="E4" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F4" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.944278128060058</v>
+        <v>1.128445195809759</v>
       </c>
       <c r="D5" t="n">
-        <v>2.005966160891206</v>
+        <v>0.325969501144821</v>
       </c>
       <c r="E5" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F5" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.987179652324484</v>
+        <v>1.135416693502729</v>
       </c>
       <c r="D6" t="n">
-        <v>8.542008283437829</v>
+        <v>1.388076346058647</v>
       </c>
       <c r="E6" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F6" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.899186476130057</v>
+        <v>1.446117802371134</v>
       </c>
       <c r="D7" t="n">
-        <v>6.996908309719808</v>
+        <v>1.136997600329469</v>
       </c>
       <c r="E7" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F7" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.096634841088143</v>
+        <v>1.478203161676823</v>
       </c>
       <c r="D8" t="n">
-        <v>12.87178249306668</v>
+        <v>2.091664655123335</v>
       </c>
       <c r="E8" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F8" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.68271582873623</v>
+        <v>1.898441322169637</v>
       </c>
       <c r="D9" t="n">
-        <v>4.628311225729872</v>
+        <v>0.7521005741811042</v>
       </c>
       <c r="E9" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F9" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.00533615997698</v>
+        <v>1.788367125996259</v>
       </c>
       <c r="D10" t="n">
-        <v>7.987917883613058</v>
+        <v>1.298036656087122</v>
       </c>
       <c r="E10" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F10" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.3513293481396</v>
+        <v>1.032091019072685</v>
       </c>
       <c r="D11" t="n">
-        <v>2.280365075122102</v>
+        <v>0.3705593247073416</v>
       </c>
       <c r="E11" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F11" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.59466079806147</v>
+        <v>3.671632379684989</v>
       </c>
       <c r="D12" t="n">
-        <v>14.43995391269556</v>
+        <v>2.346492510813028</v>
       </c>
       <c r="E12" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F12" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.87777659941074</v>
+        <v>2.092638697404246</v>
       </c>
       <c r="D13" t="n">
-        <v>4.667396806818574</v>
+        <v>0.7584519811080183</v>
       </c>
       <c r="E13" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F13" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.52927153009282</v>
+        <v>4.798506623640083</v>
       </c>
       <c r="D14" t="n">
-        <v>9.229263071457469</v>
+        <v>1.499755249111839</v>
       </c>
       <c r="E14" t="n">
-        <v>8.921241603954778</v>
+        <v>1.449701760642651</v>
       </c>
       <c r="F14" t="n">
-        <v>5.525104346847596</v>
+        <v>0.8978294563627345</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
